--- a/output/pdf_financials_xlsx/CD.xlsx
+++ b/output/pdf_financials_xlsx/CD.xlsx
@@ -5986,10 +5986,10 @@
         <v>1.433572</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.433572</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.424988</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
@@ -14648,7 +14648,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CD.xlsx
+++ b/output/pdf_financials_xlsx/CD.xlsx
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000418</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000679</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1098,40 +1098,40 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.018817</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.003901</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000833</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.002368</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000663</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.090694</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.174374</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.033537</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.031316</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.0429</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.136251</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.05141</v>
       </c>
     </row>
     <row r="13">
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.796386</v>
+        <v>-1.796804</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.924146</v>
+        <v>-0.924825</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -2114,40 +2114,40 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.795231</v>
+        <v>-2.814048</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.43832</v>
+        <v>-2.442221</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.021252</v>
+        <v>-1.022085</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.306755</v>
+        <v>-2.309123</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.730017</v>
+        <v>-0.73068</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-9.492687</v>
+        <v>-9.583380999999999</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.026028</v>
+        <v>-3.200402</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-7.218457</v>
+        <v>-7.251994</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-7.969126</v>
+        <v>-8.000442</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-5.275989</v>
+        <v>-5.318889</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-5.198672</v>
+        <v>-5.334923</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-3.22477</v>
+        <v>-3.27618</v>
       </c>
     </row>
     <row r="28">
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.796386</v>
+        <v>-1.796804</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.924146</v>
+        <v>-0.924825</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2242,40 +2242,40 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.787762</v>
+        <v>-2.806579</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.430852</v>
+        <v>-2.434753</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.018185</v>
+        <v>-1.019018</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.306755</v>
+        <v>-2.309123</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.730017</v>
+        <v>-0.73068</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-9.353923</v>
+        <v>-9.444616999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.310218</v>
+        <v>-2.484592</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-6.971709</v>
+        <v>-7.005246</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-7.722508</v>
+        <v>-7.753824</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-5.031278</v>
+        <v>-5.074178</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-4.959556</v>
+        <v>-5.095807</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.980209</v>
+        <v>-3.031619</v>
       </c>
     </row>
     <row r="30">
@@ -2540,55 +2540,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.243033</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.252609</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.002456</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.086403</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.539808</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.753055</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.169627</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.679785</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.084754</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.773923</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>11.531978</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>5.599995</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.117966</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>3.540996</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.787323</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>3.43664</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.212078</v>
       </c>
     </row>
     <row r="35">
@@ -2656,55 +2656,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.243033</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.252609</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.002456</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.086403</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.539808</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.753055</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.169627</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.679785</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.084754</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.773923</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>11.531978</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>5.599995</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.117966</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>3.540996</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.787323</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>3.43664</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.212078</v>
       </c>
     </row>
     <row r="37">
@@ -3352,55 +3352,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.243033</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.2798</v>
+        <v>0.027191</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.034718</v>
+        <v>0.032262</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.086403</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.539808</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.753055</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.189205</v>
+        <v>0.019578</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.700983</v>
+        <v>0.021198</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.099388</v>
+        <v>0.014634</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.823002</v>
+        <v>0.049079</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>11.963256</v>
+        <v>0.431278</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>5.757207</v>
+        <v>0.157212</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.438506</v>
+        <v>0.32054</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3.815909</v>
+        <v>0.274913</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.840522</v>
+        <v>0.053199</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>3.681662</v>
+        <v>0.245022</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.383825</v>
+        <v>0.171747</v>
       </c>
     </row>
     <row r="49">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
@@ -24576,7 +24576,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">

--- a/output/pdf_financials_xlsx/CD.xlsx
+++ b/output/pdf_financials_xlsx/CD.xlsx
@@ -4696,25 +4696,25 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.64286</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.365029</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.168413</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.154476</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.154477</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.175129</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.112403</v>
       </c>
     </row>
     <row r="71">
@@ -4754,25 +4754,25 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.64286</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.365029</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.168413</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.154476</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.154477</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.175129</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.112403</v>
       </c>
     </row>
     <row r="72">
@@ -4986,25 +4986,25 @@
         <v>5.725155</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>5.891859</v>
+        <v>5.248999</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.948522</v>
+        <v>0.583493</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.77258</v>
+        <v>0.604167</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.724074</v>
+        <v>0.569598</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.88173</v>
+        <v>0.727253</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.721436</v>
+        <v>0.546307</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>0.264227</v>
+        <v>0.151824</v>
       </c>
     </row>
     <row r="76">
@@ -5169,13 +5169,13 @@
         <v>0</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>0.175213</v>
       </c>
       <c r="P78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>0</v>
+        <v>0.114375</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>0</v>
@@ -5227,13 +5227,13 @@
         <v>0</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>0</v>
+        <v>0.175213</v>
       </c>
       <c r="P79" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>0</v>
+        <v>0.114375</v>
       </c>
       <c r="R79" s="3" t="n">
         <v>0</v>
@@ -5295,40 +5295,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L80" s="3" t="n">
+        <v>0.1010418218774421</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.07087643103193515</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.09655169646122923</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.1227454040606741</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>3.09548332798974</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.1166939351835617</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>-0.333707408166113</v>
       </c>
     </row>
     <row r="81">
@@ -5609,13 +5595,13 @@
         <v>1.506814</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>1.994774</v>
+        <v>1.819561</v>
       </c>
       <c r="P85" s="3" t="n">
         <v>1.420578</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>2.005656</v>
+        <v>1.891281</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>1.139371</v>
@@ -7018,16 +7004,16 @@
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.026432</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.035851</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.035851</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.058205</v>
       </c>
     </row>
     <row r="111">
@@ -7082,7 +7068,7 @@
         <v>0</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002287</v>
       </c>
       <c r="R111" s="3" t="n">
         <v>0</v>
@@ -8458,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002287</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>0</v>
@@ -8522,7 +8508,7 @@
         </is>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-5.27607</v>
+        <v>-5.278357</v>
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
@@ -9434,7 +9420,11 @@
           <t>Current portion of lease obligations 7</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -9697,7 +9687,11 @@
           <t>Lease obligations 7</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10966,7 +10960,11 @@
           <t>Lease obligations 7</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -15935,7 +15933,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -16698,7 +16700,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -18340,7 +18346,11 @@
           <t>Finder's warrants issued as fees on private placement $</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
